--- a/SO_TAY_KTV.xlsx
+++ b/SO_TAY_KTV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8402604-8381-4EC0-AFAD-454A40699D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD7DCE2-2164-497B-927E-C640614BE09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{714C7F0F-6235-4B14-8B8B-BCA2E3D6C69F}"/>
   </bookViews>
@@ -34,38 +34,312 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Triển khai dịch vụ Internet</t>
   </si>
   <si>
-    <t xml:space="preserve">Bước 1: Liên hệ khách hàng
+    <t>buoc</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>Triển khai box</t>
+  </si>
+  <si>
+    <t>Triển khai dịch vụ camera</t>
+  </si>
+  <si>
+    <t>Kí BBĐT qua Vneid</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bước 1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
  - OK =&gt; đến triển khai
  - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
-Bước 2: Checkin (Khảo sát phương án thi công, tư vấn gói cước, mô hình phù hợp =&gt; chốt phương án và số tiền thu nếu có.
-Bước 3: Triển khai dịch vụ
-Bước 4: Nghiệm thu dịch vụ (speedtest, wifianalyzer, ....)
-Bước 5: Bàn giao hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
-Bước 6: Kích thanh toán =&gt; Gen BBNT =&gt; Hoàn tất tuyến </t>
-  </si>
-  <si>
-    <t>buoc</t>
-  </si>
-  <si>
-    <t>ten</t>
+Bước 2: Khảo sát và thi công cáp (Khảo sát phương án thi công, tư vấn gói cước, mô hình phù hợp =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chốt phương án và số tiền thu nếu có.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Bước 3: Thi công tập điểm
+Bước 4: Thi công trong nhà (lưu ý vấn đề thẫm mỹ)
+Bước 5: Nghiệm thu dịch vụ (Speedtest, wifi Analyzer, Net Analyzer)
+Bước 6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
+Bước 7: Ký BBĐT =&gt; Kích thanh toán =&gt; Gen BBNT =&gt; Hoàn tất tuyến </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bước 1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
+ - OK =&gt; đến triển khai
+ - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
+Bước 2: Khảo sát phương án thi công =&gt; chốt phương án và số tiền thu nếu có.
+Bước 3: Lắp đặt Camera (lưu ý vấn đề thẫm mỹ) 
+Bước 4: Add camera vào app (đăng nhập đúng số điện thoại nếu khách hàng muốn thay đổi số thì gửi thông tin SHD - SĐT mới qua Đội Trưởng )
+Bước 4: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kí BBDT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kích thanh toán</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Member vật tư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Gen BBNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Kích hoạt cloud </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Bước 6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
+Bước 7:  Hoàn tất tuyến </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bước 1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
+ - OK =&gt; đến triển khai
+ - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
+Bước 2: Khảo sát phương án thi công =&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chốt phương án và số tiền thu nếu có.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Bước 3: Lắp đặt box (lưu ý vấn đề thẫm mỹ)
+Bước 4: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kí BBDT =&gt; Kích thanh toán =&gt; Kích hoạt box</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Bước 5: Nghiệm thu dịch vụ truyền hình
+Bước 6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
+Bước 7:  Gen BBNT =&gt; Hoàn tất tuyến </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TH1: Khách hàng có Vneid cấp 2 đăng nhập kí bình thường
+TH2: Khách hàng có Vneid cấp 1 cài ứng dụng Hifpt và có nút điều hướng qua OTP
+TH3: Khách hàng không có Vneid, không đăng nhập được ứng dụng hoặc khách hàng ở xa =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gửi thông tin nhờ đội trưởng bypass để kí qua OTP.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Thông tin gửi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Số hợp đồng - Số điện thoại - sô CCCD (Kèm hình ảnh lỗi nếu không đăng nhập được hoặc không có Vneid)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -408,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1015D3B8-B349-4BF5-896E-809717DA6DF3}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -417,18 +691,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="216" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/SO_TAY_KTV.xlsx
+++ b/SO_TAY_KTV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD7DCE2-2164-497B-927E-C640614BE09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87EF29E-705F-44C8-B4BE-8724A75BF8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{714C7F0F-6235-4B14-8B8B-BCA2E3D6C69F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Triển khai dịch vụ Internet</t>
   </si>
@@ -52,221 +52,6 @@
   </si>
   <si>
     <t>Kí BBĐT qua Vneid</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bước 1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
- - OK =&gt; đến triển khai
- - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
-Bước 2: Khảo sát và thi công cáp (Khảo sát phương án thi công, tư vấn gói cước, mô hình phù hợp =&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>chốt phương án và số tiền thu nếu có.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Bước 3: Thi công tập điểm
-Bước 4: Thi công trong nhà (lưu ý vấn đề thẫm mỹ)
-Bước 5: Nghiệm thu dịch vụ (Speedtest, wifi Analyzer, Net Analyzer)
-Bước 6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
-Bước 7: Ký BBĐT =&gt; Kích thanh toán =&gt; Gen BBNT =&gt; Hoàn tất tuyến </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bước 1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
- - OK =&gt; đến triển khai
- - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
-Bước 2: Khảo sát phương án thi công =&gt; chốt phương án và số tiền thu nếu có.
-Bước 3: Lắp đặt Camera (lưu ý vấn đề thẫm mỹ) 
-Bước 4: Add camera vào app (đăng nhập đúng số điện thoại nếu khách hàng muốn thay đổi số thì gửi thông tin SHD - SĐT mới qua Đội Trưởng )
-Bước 4: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kí BBDT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> =&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kích thanh toán</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> =&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Member vật tư</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> =&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Gen BBNT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> =&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Kích hoạt cloud </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Bước 6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
-Bước 7:  Hoàn tất tuyến </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Bước 1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
- - OK =&gt; đến triển khai
- - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
-Bước 2: Khảo sát phương án thi công =&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> chốt phương án và số tiền thu nếu có.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Bước 3: Lắp đặt box (lưu ý vấn đề thẫm mỹ)
-Bước 4: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kí BBDT =&gt; Kích thanh toán =&gt; Kích hoạt box</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Bước 5: Nghiệm thu dịch vụ truyền hình
-Bước 6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
-Bước 7:  Gen BBNT =&gt; Hoàn tất tuyến </t>
-    </r>
   </si>
   <si>
     <r>
@@ -319,6 +104,275 @@
       </rPr>
       <t xml:space="preserve"> Số hợp đồng - Số điện thoại - sô CCCD (Kèm hình ảnh lỗi nếu không đăng nhập được hoặc không có Vneid)</t>
     </r>
+  </si>
+  <si>
+    <t>Bảo hành camera</t>
+  </si>
+  <si>
+    <t>B1: Xoá camera hỏng ra khỏi app
+B2: Add camera mới vào app
+B3: Member camera bàn giao và thu hồi vào phiếu bảo trì (Lưu ý đúng số S/N) =&gt; Gen BBNT
+B4: Báo đội trưởng chuyển cloud</t>
+  </si>
+  <si>
+    <t>Đổi số điện thoại camera</t>
+  </si>
+  <si>
+    <t>Vào group HIFPT trên zalo gửi thông tin: Số hợp đồng - Số điện thoại mới - Nội dung 
+VD: HUAAA0234 - 037770126 - Khách hàng muốn đổi số điện thoại Camera nhờ a/c hỗ trợ
+Đợi DVKH hỗ trợ rồi kí BBDT gứi qua SĐT chính chủ
+Ghi chú: Trường hợp khách hàng mất số chỉnh chủ hoặc số chính chủ ko liên hệ được thì nhờ đổi luôn số chính chủ.
+VD: HUAAA0234 - 037770126 - Khách hàng muốn đổi số điện thoại chính chủ và Camera nhờ a/c hỗ trợ</t>
+  </si>
+  <si>
+    <t>Đổi số điện thoại FPT Play</t>
+  </si>
+  <si>
+    <t>Vào group HIFPT trên zalo gửi thông tin: Số hợp đồng - Số điện thoại mới - Nội dung 
+VD: HUAAA0234 - 037770126 - Khách hàng muốn đổi số điện thoại FPT Play nhờ a/c hỗ trợ
+Đợi DVKH hỗ trợ rồi kí BBDT gứi qua SĐT chính chủ
+Ghi chú: Trường hợp khách hàng mất số chỉnh chủ hoặc số chính chủ ko liên hệ được thì nhờ đổi luôn số chính chủ.
+VD: HUAAA0234 - 037770126 - Khách hàng muốn đổi số điện thoại chính chủ và FPT Play nhờ a/c hỗ trợ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
+ - OK =&gt; đến triển khai
+ - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
+B2: Khảo sát và thi công cáp (Khảo sát phương án thi công, tư vấn gói cước, mô hình phù hợp =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chốt phương án và số tiền thu nếu có.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+B3: Thi công tập điểm
+B4: Thi công trong nhà (Đảm bảo thẫm mỹ)
+B5: Nghiệm thu dịch vụ (Speedtest, wifi Analyzer, Net Analyzer)
+B6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
+B7: Ký BBĐT =&gt; Kích thanh toán =&gt; Gen BBNT =&gt; Hoàn tất tuyến </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
+ - OK =&gt; đến triển khai
+ - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
+B2: Khảo sát phương án thi công =&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chốt phương án và số tiền thu nếu có.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+B3: Lắp đặt box (Đảm bảo thẫm mỹ)
+B4: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kí BBDT =&gt; Kích thanh toán =&gt; Kích hoạt box</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+B5: Nghiệm thu dịch vụ truyền hình
+B6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
+B7:  Gen BBNT =&gt; Hoàn tất tuyến </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B1: Nhận phiếu, Liên hệ khách hàng và đến nhà checkin
+ - OK =&gt; đến triển khai
+ - Notok =&gt; xin lại lịch hẹn và tích hẹn theo yêu cầu khách hàng (ghi chú đầy đủ vào phiếu thi công)
+B2: Khảo sát phương án thi công =&gt; chốt phương án và số tiền thu nếu có.
+B3: Lắp đặt Camera (Đảm bảo thẫm mỹ) 
+B4: Add camera vào app (đăng nhập đúng số điện thoại nếu khách hàng muốn thay đổi số thì gửi thông tin SHD - SĐT mới qua Đội Trưởng )
+B4: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kí BBDT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kích thanh toán</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Member vật tư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Gen BBNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Kích hoạt cloud </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+B6: Bàn giao, hướng dẫn khách hàng sử dụng dịch vụ, ứng dụng HIFPT
+B7:  Hoàn tất tuyến </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">KPDV không đóng được phiếu triển khai báo lỗi " Dịch vụ FPT PLAY chưa kích hoạt"
+Nguyên nhân: Hệ thống đang ghi nhận 2 box 
+Xử lí: Báo dịch vụ khách hàng xoá bớt 1 box =&gt; Kí Link BBĐT gửi về số chính chủ. </t>
+  </si>
+  <si>
+    <t>KPDV có BOX lỗi " Dịch vụ FPT PLAY chưa kích hoạt"</t>
+  </si>
+  <si>
+    <t>Phiếu triển khai trả về</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không có phương án thi công =&gt; Trao đổi trực tiếp đội trưởng 
+Khách hàng đổi ý =&gt; Báo lại IBB care lại =&gt; Báo đội trưởng 
+Mô hình không phù hợp (gói cước, thiết bị) =&gt; Báo đội trưởng =&gt; Đưa ra phương án trao đổi IBB.
+Ghi chú: Tất cả phiếu triển khai phát sinh note đầy đủ thông tin vào phiếu, đội trưởng là người trực tiếp trả phiếu nếu notok </t>
+  </si>
+  <si>
+    <t>Phiếu bảo trì khách hàng huỷ</t>
+  </si>
+  <si>
+    <t>Khách hàng Không có thời gian cụ thể: Tạo SR mobile =&gt; Gủi thông tin group khu vực tag đội trưởng
+Khách hàng không đồng ý xử lí, yêu cầu huỷ: Tạo SR mobile =&gt; Gủi thông tin group "Huế Giảm Rời Mạng" tag đội trưởng và DVKH quản lí
+Ghi chú: NOTE thông tin vào phiếu đầy đủ đội trưởng là người đóng checklist</t>
   </si>
 </sst>
 </file>
@@ -682,10 +736,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1015D3B8-B349-4BF5-896E-809717DA6DF3}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -697,12 +751,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
@@ -710,7 +764,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="216" x14ac:dyDescent="0.3">
@@ -718,7 +772,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
@@ -726,7 +780,55 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/SO_TAY_KTV.xlsx
+++ b/SO_TAY_KTV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87EF29E-705F-44C8-B4BE-8724A75BF8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A6B248-3D5E-430F-85D3-B39A2550D568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{714C7F0F-6235-4B14-8B8B-BCA2E3D6C69F}"/>
   </bookViews>
@@ -54,58 +54,6 @@
     <t>Kí BBĐT qua Vneid</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">TH1: Khách hàng có Vneid cấp 2 đăng nhập kí bình thường
-TH2: Khách hàng có Vneid cấp 1 cài ứng dụng Hifpt và có nút điều hướng qua OTP
-TH3: Khách hàng không có Vneid, không đăng nhập được ứng dụng hoặc khách hàng ở xa =&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>gửi thông tin nhờ đội trưởng bypass để kí qua OTP.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Thông tin gửi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Số hợp đồng - Số điện thoại - sô CCCD (Kèm hình ảnh lỗi nếu không đăng nhập được hoặc không có Vneid)</t>
-    </r>
-  </si>
-  <si>
     <t>Bảo hành camera</t>
   </si>
   <si>
@@ -373,6 +321,58 @@
     <t>Khách hàng Không có thời gian cụ thể: Tạo SR mobile =&gt; Gủi thông tin group khu vực tag đội trưởng
 Khách hàng không đồng ý xử lí, yêu cầu huỷ: Tạo SR mobile =&gt; Gủi thông tin group "Huế Giảm Rời Mạng" tag đội trưởng và DVKH quản lí
 Ghi chú: NOTE thông tin vào phiếu đầy đủ đội trưởng là người đóng checklist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TH1: Khách hàng có Vneid cấp 2 đăng nhập kí bình thường
+TH2: Khách hàng có Vneid cấp 1 cài ứng dụng Hifpt và có nút điều hướng qua OTP
+TH3: Khách hàng không có Vneid, không đăng nhập được ứng dụng hoặc khách hàng ở xa =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gửi thông tin nhờ đội trưởng bypass để kí qua OTP.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Thông tin gửi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Số hợp đồng - Số điện thoại - Số CCCD (Kèm hình ảnh lỗi nếu không đăng nhập được hoặc không có Vneid)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
@@ -764,7 +764,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="216" x14ac:dyDescent="0.3">
@@ -772,7 +772,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
@@ -780,55 +780,55 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/SO_TAY_KTV.xlsx
+++ b/SO_TAY_KTV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A6B248-3D5E-430F-85D3-B39A2550D568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98FFDC7-69D6-4249-8A90-7EF00F1C429B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{714C7F0F-6235-4B14-8B8B-BCA2E3D6C69F}"/>
   </bookViews>
@@ -309,12 +309,6 @@
     <t>Phiếu triển khai trả về</t>
   </si>
   <si>
-    <t xml:space="preserve">Không có phương án thi công =&gt; Trao đổi trực tiếp đội trưởng 
-Khách hàng đổi ý =&gt; Báo lại IBB care lại =&gt; Báo đội trưởng 
-Mô hình không phù hợp (gói cước, thiết bị) =&gt; Báo đội trưởng =&gt; Đưa ra phương án trao đổi IBB.
-Ghi chú: Tất cả phiếu triển khai phát sinh note đầy đủ thông tin vào phiếu, đội trưởng là người trực tiếp trả phiếu nếu notok </t>
-  </si>
-  <si>
     <t>Phiếu bảo trì khách hàng huỷ</t>
   </si>
   <si>
@@ -373,6 +367,12 @@
       </rPr>
       <t xml:space="preserve"> Số hợp đồng - Số điện thoại - Số CCCD (Kèm hình ảnh lỗi nếu không đăng nhập được hoặc không có Vneid)</t>
     </r>
+  </si>
+  <si>
+    <t>Không có phương án thi công =&gt; Trao đổi trực tiếp đội trưởng 
+Khách hàng đổi ý =&gt; Báo lại IBB care lại =&gt; Báo đội trưởng 
+Mô hình không phù hợp (gói cước, thiết bị) =&gt; Báo đội trưởng =&gt; Đưa ra phương án trao đổi IBB.
+Ghi chú: Tất cả phiếu triển khai phát sinh note đầy đủ thông tin vào phiếu, đội trưởng là người trực tiếp trả phiếu.</t>
   </si>
 </sst>
 </file>
@@ -780,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72" x14ac:dyDescent="0.3">
@@ -820,15 +820,15 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
